--- a/result.xlsx
+++ b/result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UIT - Nam 1\Cau truc du lieu và giai thuat\BT 01-26 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ACA858-7D3A-4B0F-B403-A6CFA7429CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6673CC-B3BD-4AD3-82C2-6D727D916D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
     <t>Heapsort</t>
   </si>
   <si>
-    <t>Cppsort</t>
-  </si>
-  <si>
-    <t>Numpy sort</t>
-  </si>
-  <si>
     <t>test1</t>
   </si>
   <si>
@@ -73,6 +67,12 @@
   </si>
   <si>
     <t>avg</t>
+  </si>
+  <si>
+    <t>sort (C++)</t>
+  </si>
+  <si>
+    <t>sort (Numpy)</t>
   </si>
 </sst>
 </file>
@@ -411,15 +411,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>3090</v>
@@ -439,7 +439,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2990</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>3741</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>3732</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>4024</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>4038</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>3861</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>3479</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>3493</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>3624</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <f>AVERAGE(B2:B11)</f>

--- a/result.xlsx
+++ b/result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UIT - Nam 1\Cau truc du lieu và giai thuat\BT 01-26 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6673CC-B3BD-4AD3-82C2-6D727D916D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D793531-C0D1-4F74-A1CD-6519E8F323BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -422,19 +422,19 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>3090</v>
+        <v>3885</v>
       </c>
       <c r="C2">
-        <v>4866</v>
+        <v>9047</v>
       </c>
       <c r="D2">
-        <v>7110</v>
+        <v>27127</v>
       </c>
       <c r="E2">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -442,19 +442,19 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>2990</v>
+        <v>4297</v>
       </c>
       <c r="C3">
-        <v>4463</v>
+        <v>9078</v>
       </c>
       <c r="D3">
-        <v>5174</v>
+        <v>17555</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -462,19 +462,19 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>3741</v>
+        <v>5203</v>
       </c>
       <c r="C4">
-        <v>5940</v>
+        <v>11269</v>
       </c>
       <c r="D4">
-        <v>7472</v>
+        <v>17842</v>
       </c>
       <c r="E4">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -482,19 +482,19 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>3732</v>
+        <v>5552</v>
       </c>
       <c r="C5">
-        <v>5946</v>
+        <v>11441</v>
       </c>
       <c r="D5">
-        <v>7317</v>
+        <v>18235</v>
       </c>
       <c r="E5">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -502,16 +502,16 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>4024</v>
+        <v>5482</v>
       </c>
       <c r="C6">
-        <v>5988</v>
+        <v>11343</v>
       </c>
       <c r="D6">
-        <v>7004</v>
+        <v>17705</v>
       </c>
       <c r="E6">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="F6">
         <v>25</v>
@@ -522,19 +522,19 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4038</v>
+        <v>5543</v>
       </c>
       <c r="C7">
-        <v>5824</v>
+        <v>11820</v>
       </c>
       <c r="D7">
-        <v>7714</v>
+        <v>19671</v>
       </c>
       <c r="E7">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -542,19 +542,19 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>3861</v>
+        <v>5907</v>
       </c>
       <c r="C8">
-        <v>6054</v>
+        <v>12173</v>
       </c>
       <c r="D8">
-        <v>6345</v>
+        <v>18652</v>
       </c>
       <c r="E8">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -562,19 +562,19 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>3479</v>
+        <v>5429</v>
       </c>
       <c r="C9">
-        <v>5553</v>
+        <v>12429</v>
       </c>
       <c r="D9">
-        <v>6869</v>
+        <v>20370</v>
       </c>
       <c r="E9">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -582,19 +582,19 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>3493</v>
+        <v>5641</v>
       </c>
       <c r="C10">
-        <v>5903</v>
+        <v>11418</v>
       </c>
       <c r="D10">
-        <v>5745</v>
+        <v>20113</v>
       </c>
       <c r="E10">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -602,19 +602,19 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>3624</v>
+        <v>5706</v>
       </c>
       <c r="C11">
-        <v>6105</v>
+        <v>12308</v>
       </c>
       <c r="D11">
-        <v>7312</v>
+        <v>19949</v>
       </c>
       <c r="E11">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -623,23 +623,23 @@
       </c>
       <c r="B12">
         <f>AVERAGE(B2:B11)</f>
-        <v>3607.2</v>
+        <v>5264.5</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:F12" si="0">AVERAGE(C2:C11)</f>
-        <v>5664.2</v>
+        <v>11232.6</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>6806.2</v>
+        <v>19721.900000000001</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>95.8</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>26.1</v>
+        <v>27.5</v>
       </c>
     </row>
   </sheetData>
